--- a/Solutions/Igneous.xlsx
+++ b/Solutions/Igneous.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hansj\Dropbox\Thermolab\v_26_02_23\Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hans\Documents\GitHub\Thermolab\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C76217-E107-494F-8383-AB34CD22ED3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="865" activeTab="2" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="16710" yWindow="2270" windowWidth="22460" windowHeight="16660" tabRatio="865" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt(G25)" sheetId="4" r:id="rId1"/>
